--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:54:19+00:00</t>
+    <t>2026-09-01T20:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="306">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:22:52+00:00</t>
+    <t>2026-09-01T21:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -586,10 +586,7 @@
     <t>ResearchSubject.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -605,10 +602,13 @@
 </t>
   </si>
   <si>
-    <t>Register, an dem teilgenommen wird</t>
-  </si>
-  <si>
-    <t>Verweis auf das Register, an dem die Person teilnimmt, als Library nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Notwendig, weil ResearchSubject.study nur auf ResearchStudy zeigen kann, das Modul Studie ein Register aber als Library modelliert.</t>
+    <t>Katalogeintrag des Registers als Library (optional)</t>
+  </si>
+  <si>
+    <t>Optionaler Verweis auf den Library-Katalogeintrag des Registers nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Der verbindliche Registerbezug laeuft ueber ResearchSubject.study, das in R4 zwingend auf eine ResearchStudy zeigt.</t>
+  </si>
+  <si>
+    <t>Optionaler Verweis auf den Library-Katalogeintrag nach mii-pr-studie-register. Der verbindliche Registerbezug laeuft ueber study, weil R4 das so erzwingt.</t>
   </si>
   <si>
     <t>ResearchSubject.modifierExtension</t>
@@ -922,13 +922,13 @@
 </t>
   </si>
   <si>
-    <t>Nur zu setzen, wenn das Register zusätzlich als ResearchStudy geführt wird</t>
+    <t>Das Register, als ResearchStudy gefuehrt</t>
   </si>
   <si>
     <t>Referenz auf die Studie, an der der Proband teilnimmt</t>
   </si>
   <si>
-    <t>Siehe Kopfkommentar: der eigentliche Registerbezug läuft über die Extension 'register', weil ResearchSubject.study nicht auf eine Library zeigen kann.</t>
+    <t>In R4 ist study 1..1 Pflicht und auf ResearchStudy festgelegt. Ein Register muss daher als ResearchStudy vorliegen; der Library-Katalogeintrag des Moduls Studie kann hier nicht stehen. Siehe Kopfkommentar.</t>
   </si>
   <si>
     <t>ResearchSubject.individual</t>
@@ -2980,11 +2980,11 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
@@ -3002,12 +3002,14 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3056,7 +3058,7 @@
         <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3073,20 +3075,20 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>83</v>
@@ -3101,15 +3103,17 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3158,7 +3162,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:34:57+00:00</t>
+    <t>2026-09-01T21:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:46:35+00:00</t>
+    <t>2026-09-02T02:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T02:40:35+00:00</t>
+    <t>2026-09-02T02:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
